--- a/branches/main/StructureDefinition-mii-pr-icu-vent-eingestellter-inspiratorischer-gasfluss.xlsx
+++ b/branches/main/StructureDefinition-mii-pr-icu-vent-eingestellter-inspiratorischer-gasfluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T11:25:36+00:00</t>
+    <t>2026-10-21T14:50:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/main/StructureDefinition-mii-pr-icu-vent-eingestellter-inspiratorischer-gasfluss.xlsx
+++ b/branches/main/StructureDefinition-mii-pr-icu-vent-eingestellter-inspiratorischer-gasfluss.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.3</t>
+    <t>2027.0.0-ballot.3-rc.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:50:03+00:00</t>
+    <t>2026-10-30T08:50:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
